--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\megmu\source\repos\megmuni\ABM-Random-Forest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-Random-Forest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C52D6A8-10C0-4745-BC43-78D0FC9F75A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504325C3-5D65-446C-B0DF-D439C97FDFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="14">
-  <si>
-    <t>Parameter Number/Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="82">
   <si>
     <t>Mean</t>
   </si>
@@ -77,6 +74,213 @@
   </si>
   <si>
     <t>Upper</t>
+  </si>
+  <si>
+    <t>Parameter Number</t>
+  </si>
+  <si>
+    <t>Parameter Name</t>
+  </si>
+  <si>
+    <t>cell:proliferation:hours_between_proliferation</t>
+  </si>
+  <si>
+    <t>cell:proliferation:tgf_threshold</t>
+  </si>
+  <si>
+    <t>cell:proliferation:log_scale</t>
+  </si>
+  <si>
+    <t>cell:proliferation:log_offset</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:tgf_baseline</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:tgf_feedback_tgf</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:tgf_feedback_il1beta</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:tgf_feedback_tnf</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:tnf_baseline</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:tnf_feedback_il1beta</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:tnf_feedback_tgf_denom</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:il1beta_baseline</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:il1beta_feedback_tnf</t>
+  </si>
+  <si>
+    <t>cell:cytokine_synthesis:il1beta_feedback_tgf_denom</t>
+  </si>
+  <si>
+    <t>stem:ocr_fmol_per_hour_per_cell</t>
+  </si>
+  <si>
+    <t>stem:apoptosis_chance</t>
+  </si>
+  <si>
+    <t>stem:migration:elasticity_effect</t>
+  </si>
+  <si>
+    <t>stem:migration:baseline_speed</t>
+  </si>
+  <si>
+    <t>stem:cytokine_synthesis:tgf_baseline</t>
+  </si>
+  <si>
+    <t>stem:cytokine_synthesis:tnf_baseline</t>
+  </si>
+  <si>
+    <t>stem:cytokine_synthesis:il1beta_baseline</t>
+  </si>
+  <si>
+    <t>stem:collagen_synthesis:baseline_rate</t>
+  </si>
+  <si>
+    <t>stem:aggrecan_synthesis:tgf_threshold</t>
+  </si>
+  <si>
+    <t>stem:proliferation:tgf_threshold</t>
+  </si>
+  <si>
+    <t>stem:proliferation:tnf_effect</t>
+  </si>
+  <si>
+    <t>stem:proliferation:il1beta_effect</t>
+  </si>
+  <si>
+    <t>stem:proliferation:elasticity_effect</t>
+  </si>
+  <si>
+    <t>stem:differentiation:asymmetric_probability</t>
+  </si>
+  <si>
+    <t>stem:differentiation:baseline_probability</t>
+  </si>
+  <si>
+    <t>stem:differentiation:tgf_effect</t>
+  </si>
+  <si>
+    <t>stem:differentiation:hours_between_attempts</t>
+  </si>
+  <si>
+    <t>progen:ocr_fmol_per_hour_per_cell</t>
+  </si>
+  <si>
+    <t>progen:apoptosis_chance</t>
+  </si>
+  <si>
+    <t>progen:migration:elasticity_effect</t>
+  </si>
+  <si>
+    <t>progen:migration:baseline_speed</t>
+  </si>
+  <si>
+    <t>progen:cytokine_synthesis:tgf_baseline</t>
+  </si>
+  <si>
+    <t>progen:cytokine_synthesis:tnf_baseline</t>
+  </si>
+  <si>
+    <t>progen:cytokine_synthesis:il1beta_baseline</t>
+  </si>
+  <si>
+    <t>progen:aggrecan_synthesis:baseline_rate</t>
+  </si>
+  <si>
+    <t>np:ocr_fmol_per_hour_per_cell</t>
+  </si>
+  <si>
+    <t>np:apoptosis_chance</t>
+  </si>
+  <si>
+    <t>np:migration:elasticity_effect</t>
+  </si>
+  <si>
+    <t>np:migration:baseline_speed</t>
+  </si>
+  <si>
+    <t>np:collagen_synthesis:scaling_factor</t>
+  </si>
+  <si>
+    <t>np:collagen_synthesis:time_effect</t>
+  </si>
+  <si>
+    <t>np:collagen_synthesis:baseline_rate</t>
+  </si>
+  <si>
+    <t>np:aggrecan_synthesis:scaling_factor</t>
+  </si>
+  <si>
+    <t>np:aggrecan_synthesis:time_effect</t>
+  </si>
+  <si>
+    <t>np:aggrecan_synthesis:baseline_rate</t>
+  </si>
+  <si>
+    <t>biomaterial:elastic_modulus:intercept</t>
+  </si>
+  <si>
+    <t>biomaterial:elastic_modulus:alginate_concentration</t>
+  </si>
+  <si>
+    <t>biomaterial:elastic_modulus:crosslinker_density</t>
+  </si>
+  <si>
+    <t>biomaterial:elastic_modulus:alginate_molecular_weight</t>
+  </si>
+  <si>
+    <t>biomaterial:elastic_modulus:alginate_crosslinker_interaction</t>
+  </si>
+  <si>
+    <t>biomaterial:elastic_modulus:alginate_mw_interaction</t>
+  </si>
+  <si>
+    <t>biomaterial:elastic_modulus:mw_crosslinker_interaction</t>
+  </si>
+  <si>
+    <t>biomaterial:pore_size:crosslinker_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:pore_size:baseline</t>
+  </si>
+  <si>
+    <t>biomaterial:mass_loss:baseline</t>
+  </si>
+  <si>
+    <t>biomaterial:mass_loss:crosslinker_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:mass_loss:time_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:mass_loss:crosslinker_time_interaction</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:baseline</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:time_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:alginate_concentration_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:time_crosslinker_interaction</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:alginate_crosslinker_interaction</t>
   </si>
 </sst>
 </file>
@@ -443,1604 +647,1808 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J68"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K68"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="1" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+      <c r="D2">
+        <f>(F2-E2)/4</f>
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2">
+        <v>25</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>24</v>
-      </c>
-      <c r="C2">
-        <f>(E2-D2)/4</f>
-        <v>0.5</v>
-      </c>
-      <c r="D2" s="2">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2">
-        <v>25</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>10</v>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C50" si="0">(E3-D3)/4</f>
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D50" si="0">(F3-E3)/4</f>
         <v>24.75</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>100</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
         <f t="shared" si="0"/>
         <v>0.24975</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1E-3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>2</v>
       </c>
-      <c r="J4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>18</v>
       </c>
       <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <f t="shared" si="0"/>
         <v>0.24975</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>1E-3</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
       <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>3</v>
       </c>
-      <c r="J5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>10</v>
+      <c r="B6" t="s">
+        <v>19</v>
       </c>
       <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
         <f t="shared" si="0"/>
         <v>12.25</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>50</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="I6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>4</v>
       </c>
-      <c r="J6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
         <v>0.05</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <f t="shared" si="0"/>
         <v>0.24975</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>1E-3</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>10</v>
+      <c r="B8" t="s">
+        <v>21</v>
       </c>
       <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
         <f t="shared" si="0"/>
         <v>12.25</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>50</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
         <v>5</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
       <c r="E9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
         <v>2.4</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
       <c r="E10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
         <v>4</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
       <c r="E11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
       <c r="E12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13">
         <v>5</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
       <c r="E13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>1</v>
+      <c r="B14" t="s">
+        <v>27</v>
       </c>
       <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
       <c r="E14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
         <v>3.2</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
       <c r="E15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16">
         <v>104.65</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <f t="shared" si="0"/>
         <v>112.5</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>50</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="2">
         <v>500</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17">
         <v>0.1</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <f t="shared" si="0"/>
         <v>0.24975</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>1E-3</v>
       </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
       <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18">
         <v>0.11</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <f t="shared" si="0"/>
         <v>0.27225000000000005</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="2">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19">
         <v>0.35</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <f t="shared" si="0"/>
         <v>0.86624999999999996</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="2">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="2">
         <v>3.5</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20">
         <v>5</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
       <c r="E20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>0</v>
+      <c r="B21" t="s">
+        <v>34</v>
       </c>
       <c r="C21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>0</v>
+      <c r="B22" t="s">
+        <v>35</v>
       </c>
       <c r="C22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>10</v>
+      <c r="B23" t="s">
+        <v>36</v>
       </c>
       <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
         <f t="shared" si="0"/>
         <v>24.75</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
       <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
         <v>100</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24">
         <v>100000</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <f t="shared" si="0"/>
         <v>247500</v>
       </c>
-      <c r="D24" s="2">
+      <c r="E24" s="2">
         <v>10000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000000</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25">
-        <v>10</v>
+      <c r="B25" t="s">
+        <v>38</v>
       </c>
       <c r="C25">
+        <v>10</v>
+      </c>
+      <c r="D25">
         <f t="shared" si="0"/>
         <v>24.75</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
       <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
         <v>100</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26">
         <v>0.8</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <f t="shared" si="0"/>
         <v>0.24975</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>1E-3</v>
       </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
       <c r="F26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27">
         <v>1E-3</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <f t="shared" si="0"/>
         <v>0.24975</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>1E-3</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
       <c r="F27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28">
         <v>0.5</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <f t="shared" si="0"/>
         <v>2.4997500000000001</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>1E-3</v>
       </c>
-      <c r="E28">
-        <v>10</v>
-      </c>
       <c r="F28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29">
         <v>0.7</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <f t="shared" si="0"/>
         <v>5.0000000000000017E-2</v>
       </c>
-      <c r="D29" s="2">
+      <c r="E29" s="2">
         <v>0.6</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F29" s="2">
         <v>0.8</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>4</v>
       </c>
-      <c r="G29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30">
         <v>0.5</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <f t="shared" si="0"/>
         <v>4.9999999999999989E-2</v>
       </c>
-      <c r="D30" s="2">
+      <c r="E30" s="2">
         <v>0.4</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F30" s="2">
         <v>0.6</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>4</v>
       </c>
-      <c r="G30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31">
         <v>1E-3</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <f t="shared" si="0"/>
         <v>0.24975</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>1E-3</v>
       </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
       <c r="F31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32">
         <v>48</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="D32" s="2">
+      <c r="E32" s="2">
         <v>47</v>
       </c>
-      <c r="E32" s="2">
+      <c r="F32" s="2">
         <v>49</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33">
         <v>30.46</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <f t="shared" si="0"/>
         <v>22.5</v>
       </c>
-      <c r="D33" s="2">
-        <v>10</v>
-      </c>
       <c r="E33" s="2">
+        <v>10</v>
+      </c>
+      <c r="F33" s="2">
         <v>100</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34">
         <v>0.1</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <f t="shared" si="0"/>
         <v>0.24975</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>1E-3</v>
       </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
       <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35">
         <v>0.11</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <f t="shared" si="0"/>
         <v>0.27225000000000005</v>
       </c>
-      <c r="D35" s="2">
+      <c r="E35" s="2">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F35" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36">
         <v>0.83</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <f t="shared" si="0"/>
         <v>2.0542500000000001</v>
       </c>
-      <c r="D36" s="2">
+      <c r="E36" s="2">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="E36" s="2">
+      <c r="F36" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37">
-        <v>1</v>
+      <c r="B37" t="s">
+        <v>50</v>
       </c>
       <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
       <c r="E37">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38">
         <v>2.58</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
       <c r="E38">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39">
-        <v>0</v>
+      <c r="B39" t="s">
+        <v>52</v>
       </c>
       <c r="C39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40">
-        <v>1</v>
+      <c r="B40" t="s">
+        <v>53</v>
       </c>
       <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
       <c r="E40">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41">
         <v>15.31</v>
       </c>
-      <c r="C41">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
       <c r="D41">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41">
         <v>50</v>
       </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42">
         <v>5</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
       <c r="E42">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F42">
+        <v>10</v>
+      </c>
+      <c r="G42">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43">
         <v>0.11</v>
       </c>
-      <c r="C43">
-        <f t="shared" ref="C43" si="1">(E43-D43)/4</f>
+      <c r="D43">
+        <f t="shared" ref="D43" si="1">(F43-E43)/4</f>
         <v>0.27225000000000005</v>
       </c>
-      <c r="D43" s="2">
+      <c r="E43" s="2">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="E43" s="2">
+      <c r="F43" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44">
         <v>1.3</v>
       </c>
-      <c r="C44">
-        <f>(E44-D44)/4</f>
+      <c r="D44">
+        <f>(F44-E44)/4</f>
         <v>3.2174999999999998</v>
       </c>
-      <c r="D44" s="2">
+      <c r="E44" s="2">
         <v>0.13</v>
       </c>
-      <c r="E44" s="2">
+      <c r="F44" s="2">
         <v>13</v>
       </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="1">
-        <v>10</v>
-      </c>
-      <c r="C45">
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="1">
+        <v>10</v>
+      </c>
+      <c r="D45">
         <f t="shared" si="0"/>
         <v>24.75</v>
       </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
       <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
         <v>100</v>
       </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="1">
         <v>6.45</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <f t="shared" si="0"/>
         <v>15.963749999999999</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>0.64500000000000002</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>64.5</v>
       </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="1">
         <v>3.6</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <f t="shared" si="0"/>
         <v>8.91</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>0.36</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>36</v>
       </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="1">
         <v>20</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <f t="shared" si="0"/>
         <v>49.5</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>2</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>200</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="1">
         <v>38</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <f t="shared" si="0"/>
         <v>94.05</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>3.8</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>380</v>
       </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="1">
         <v>16.600000000000001</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <f t="shared" si="0"/>
         <v>41.085000000000001</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>1.66</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>166</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51">
         <v>125</v>
       </c>
-      <c r="C51">
-        <f t="shared" ref="C51:C68" si="2">(E51-D51)/4</f>
-        <v>0</v>
-      </c>
       <c r="D51">
-        <f>B51</f>
+        <f t="shared" ref="D51:D68" si="2">(F51-E51)/4</f>
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <f>C51</f>
         <v>125</v>
       </c>
-      <c r="E51">
-        <f>B51</f>
+      <c r="F51">
+        <f>C51</f>
         <v>125</v>
       </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>11</v>
-      </c>
-      <c r="I51" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>10</v>
+      </c>
+      <c r="J51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52">
         <v>58</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D52">
-        <f t="shared" ref="D52:D68" si="3">B52</f>
+      <c r="E52">
+        <f t="shared" ref="E52:E68" si="3">C52</f>
         <v>58</v>
       </c>
-      <c r="E52">
-        <f t="shared" ref="E52:E68" si="4">B52</f>
+      <c r="F52">
+        <f t="shared" ref="F52:F68" si="4">C52</f>
         <v>58</v>
       </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53">
         <v>971</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <f t="shared" si="3"/>
         <v>971</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <f t="shared" si="4"/>
         <v>971</v>
       </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54">
         <v>1.0369999999999999</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <f t="shared" si="3"/>
         <v>1.0369999999999999</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <f t="shared" si="4"/>
         <v>1.0369999999999999</v>
       </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55">
         <v>756</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <f t="shared" si="3"/>
         <v>756</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <f t="shared" si="4"/>
         <v>756</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56">
         <v>0.51600000000000001</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <f t="shared" si="3"/>
         <v>0.51600000000000001</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <f t="shared" si="4"/>
         <v>0.51600000000000001</v>
       </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57">
         <v>0.16500000000000001</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <f t="shared" si="3"/>
         <v>0.16500000000000001</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <f t="shared" si="4"/>
         <v>0.16500000000000001</v>
       </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58">
         <v>1769.8</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <f t="shared" si="3"/>
         <v>1769.8</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <f t="shared" si="4"/>
         <v>1769.8</v>
       </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-      <c r="G58" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="s">
+        <v>72</v>
+      </c>
+      <c r="C59">
         <v>258.5</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <f t="shared" si="3"/>
         <v>258.5</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <f t="shared" si="4"/>
         <v>258.5</v>
       </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60">
         <v>0.23400000000000001</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <f t="shared" si="3"/>
         <v>0.23400000000000001</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <f t="shared" si="4"/>
         <v>0.23400000000000001</v>
       </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
-      <c r="G60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61">
         <v>7.7850000000000001</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <f t="shared" si="3"/>
         <v>7.7850000000000001</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <f t="shared" si="4"/>
         <v>7.7850000000000001</v>
       </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-      <c r="G61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62">
         <v>0.15</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <f t="shared" si="4"/>
         <v>0.15</v>
       </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63">
         <v>1.36</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <f t="shared" si="3"/>
         <v>1.36</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <f t="shared" si="4"/>
         <v>1.36</v>
       </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64">
         <v>72.477999999999994</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <f t="shared" si="3"/>
         <v>72.477999999999994</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <f t="shared" si="4"/>
         <v>72.477999999999994</v>
       </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-      <c r="G64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="s">
+        <v>78</v>
+      </c>
+      <c r="C65">
         <v>0.13100000000000001</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <f t="shared" si="3"/>
         <v>0.13100000000000001</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <f t="shared" si="4"/>
         <v>0.13100000000000001</v>
       </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
-      <c r="G65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66">
         <v>22.033999999999999</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <f t="shared" si="3"/>
         <v>22.033999999999999</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <f t="shared" si="4"/>
         <v>22.033999999999999</v>
       </c>
-      <c r="F66">
-        <v>1</v>
-      </c>
-      <c r="G66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67">
         <v>3.2839999999999998</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <f t="shared" si="3"/>
         <v>3.2839999999999998</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <f t="shared" si="4"/>
         <v>3.2839999999999998</v>
       </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68">
         <v>35.752000000000002</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <f t="shared" si="3"/>
         <v>35.752000000000002</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <f t="shared" si="4"/>
         <v>35.752000000000002</v>
       </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68" t="s">
-        <v>11</v>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
